--- a/data/Heat map 4-2 Recognition and Reputation.xlsx
+++ b/data/Heat map 4-2 Recognition and Reputation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{916A02E6-EFF3-4257-A6BD-B82D848EA202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A227C5D-2AE0-4AC5-8E92-B54C3BDD4B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Res, Cap &amp; Products – KPI #" sheetId="1" r:id="rId1"/>
@@ -173,18 +173,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -205,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -354,21 +348,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color indexed="64"/>
       </left>
@@ -446,6 +425,80 @@
       </right>
       <top/>
       <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -456,36 +509,30 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -505,107 +552,116 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -911,658 +967,654 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B183A326-557F-46A5-AEA8-D42BBCF0052C}">
-  <dimension ref="B1:U19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.21875" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="29" t="s">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="52"/>
+    </row>
+    <row r="2" spans="1:20" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="41"/>
-    </row>
-    <row r="2" spans="2:21" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="26" t="s">
+      <c r="B2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="26" t="s">
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="26" t="s">
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="28"/>
-    </row>
-    <row r="3" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="30"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="42" t="s">
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="54"/>
+    </row>
+    <row r="3" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="43"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="D3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="E3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="G3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="I3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="J3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="K3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="L3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="M3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="N3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="O3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="P3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="Q3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="R3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="12" t="s">
+      <c r="S3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="T3" s="41" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="23" t="s">
+    <row r="4" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="33">
+      <c r="C4" s="20">
         <v>17</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="43" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="33">
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="20">
         <v>1</v>
       </c>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="16"/>
-    </row>
-    <row r="5" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="24"/>
-      <c r="C5" s="4" t="s">
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="14"/>
+    </row>
+    <row r="5" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="48"/>
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="34">
+      <c r="C5" s="21">
         <v>23</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="44" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14"/>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="17"/>
-    </row>
-    <row r="6" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="24"/>
-      <c r="C6" s="4" t="s">
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="21">
+        <v>0</v>
+      </c>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="15"/>
+    </row>
+    <row r="6" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48"/>
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="34">
+      <c r="C6" s="21">
         <v>19</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="44" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="17"/>
-    </row>
-    <row r="7" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="25"/>
-      <c r="C7" s="5" t="s">
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="21">
+        <v>0</v>
+      </c>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="12"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="15"/>
+    </row>
+    <row r="7" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="49"/>
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="35">
-        <v>0</v>
-      </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="45">
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="37"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="28">
         <v>14</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="35">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="22">
         <v>3</v>
       </c>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="20"/>
-    </row>
-    <row r="8" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="17"/>
+    </row>
+    <row r="8" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="33">
+      <c r="C8" s="38">
         <v>18</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="43">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="26">
         <v>1</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="33">
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="20">
         <v>3</v>
       </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="16"/>
-    </row>
-    <row r="9" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="24"/>
-      <c r="C9" s="4" t="s">
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="14"/>
+    </row>
+    <row r="9" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="48"/>
+      <c r="B9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="34">
+      <c r="C9" s="21">
         <v>43</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="44">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="27">
         <v>17</v>
       </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="17"/>
-    </row>
-    <row r="10" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="24"/>
-      <c r="C10" s="4" t="s">
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="21">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="15"/>
+    </row>
+    <row r="10" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="48"/>
+      <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="34">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="44">
+      <c r="C10" s="21">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="27">
         <v>3</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="17"/>
-    </row>
-    <row r="11" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="25"/>
-      <c r="C11" s="5" t="s">
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="21">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="15"/>
+    </row>
+    <row r="11" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="49"/>
+      <c r="B11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="35">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="45">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="19"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="20"/>
-    </row>
-    <row r="12" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="23" t="s">
+      <c r="C11" s="22">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="28">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="22">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="17"/>
+    </row>
+    <row r="12" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="33">
+      <c r="C12" s="20">
         <v>7</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="43">
-        <v>0</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="33">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="16"/>
-    </row>
-    <row r="13" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="24"/>
-      <c r="C13" s="4" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="26">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="20">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="14"/>
+    </row>
+    <row r="13" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="48"/>
+      <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="34">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="44">
-        <v>0</v>
-      </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="17"/>
-    </row>
-    <row r="14" spans="2:21" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="24"/>
-      <c r="C14" s="4" t="s">
+      <c r="C13" s="21">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="27">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="21">
+        <v>0</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="15"/>
+    </row>
+    <row r="14" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="34">
+      <c r="C14" s="21">
         <v>6</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="44">
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="27">
         <v>3</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="17"/>
-    </row>
-    <row r="15" spans="2:21" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="24"/>
-      <c r="C15" s="4" t="s">
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="21">
+        <v>0</v>
+      </c>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="15"/>
+    </row>
+    <row r="15" spans="1:20" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="48"/>
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="34">
+      <c r="C15" s="21">
         <v>7</v>
       </c>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="44">
-        <v>0</v>
-      </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="17"/>
-    </row>
-    <row r="16" spans="2:21" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="25"/>
-      <c r="C16" s="5" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="27">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="21">
+        <v>0</v>
+      </c>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="15"/>
+    </row>
+    <row r="16" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="49"/>
+      <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="34">
-        <v>0</v>
-      </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="44">
-        <v>0</v>
-      </c>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="34">
+      <c r="C16" s="21">
+        <v>0</v>
+      </c>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="27">
+        <v>0</v>
+      </c>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="21">
         <v>1</v>
       </c>
-      <c r="Q16" s="46"/>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46"/>
-      <c r="T16" s="46"/>
-      <c r="U16" s="47"/>
-    </row>
-    <row r="17" spans="2:21" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7" t="s">
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="30"/>
+    </row>
+    <row r="17" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="36">
+      <c r="C17" s="23">
         <v>30</v>
       </c>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="48"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="50">
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33">
         <v>25</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="36">
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="23">
         <v>30</v>
       </c>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="49"/>
-    </row>
-    <row r="18" spans="2:21" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9" t="s">
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="32"/>
+    </row>
+    <row r="18" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="37">
-        <f>SUM(D4:D16)</f>
+      <c r="C18" s="24">
+        <f>SUM(C4:C16)</f>
         <v>140</v>
       </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="37">
-        <f>SUM(J4:J16)</f>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="24">
+        <f>SUM(I4:I16)</f>
         <v>38</v>
       </c>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="37">
-        <f>SUM(P4:P16)</f>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="24">
+        <f>SUM(O4:O16)</f>
         <v>8</v>
       </c>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="52"/>
-    </row>
-    <row r="19" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="10"/>
-      <c r="C19" s="11" t="s">
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="35"/>
+    </row>
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="38">
+      <c r="C19" s="25">
         <v>2.3076923076923075</v>
       </c>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="53">
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="36">
         <v>1.9230769230769231</v>
       </c>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="38">
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="25">
         <v>2.3076923076923075</v>
       </c>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="22"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D1:U1"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="B4:B7"/>
+  <mergeCells count="7">
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="C1:T1"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A7"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D16">
+  <conditionalFormatting sqref="C4:C7 C9:C16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$C$19/2"/>
-        <cfvo type="formula" val="$C$19"/>
+        <cfvo type="formula" val="$B$19/2"/>
+        <cfvo type="formula" val="$B$19"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J16">
+  <conditionalFormatting sqref="I4:I16">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$I$19/2"/>
-        <cfvo type="formula" val="$I$19"/>
+        <cfvo type="formula" val="$H$19/2"/>
+        <cfvo type="formula" val="$H$19"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P16">
+  <conditionalFormatting sqref="O4:O16">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="formula" val="$O$19/2"/>
-        <cfvo type="formula" val="$O$19"/>
+        <cfvo type="formula" val="$N$19/2"/>
+        <cfvo type="formula" val="$N$19"/>
         <color rgb="FFFF0000"/>
         <color rgb="FFFFFF00"/>
         <color rgb="FF00B050"/>
@@ -1571,6 +1623,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C18 O18" formulaRange="1"/>
+    <ignoredError sqref="C3:T3" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 

--- a/data/Heat map 4-2 Recognition and Reputation.xlsx
+++ b/data/Heat map 4-2 Recognition and Reputation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863705E7-DE6F-45EC-A9F8-BA0371B25F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF828658-3A8A-4F08-885C-CEBE3D0559BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -558,7 +558,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -595,6 +595,81 @@
     <xf numFmtId="1" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -634,86 +709,21 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1019,69 +1029,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B183A326-557F-46A5-AEA8-D42BBCF0052C}">
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.21875" customWidth="1"/>
     <col min="2" max="2" width="31.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="8.88671875" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="17" t="s">
+    <row r="1" spans="1:25" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="19"/>
-    </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="28" t="s">
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+    </row>
+    <row r="2" spans="1:25" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="14" t="s">
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="14" t="s">
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="16"/>
-    </row>
-    <row r="3" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26"/>
-      <c r="B3" s="27"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+    </row>
+    <row r="3" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="51"/>
+      <c r="B3" s="53"/>
       <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
@@ -1136,406 +1157,476 @@
       <c r="T3" s="13" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+    </row>
+    <row r="4" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="48" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="17">
         <v>17</v>
       </c>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="33" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="38">
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="22">
         <v>1</v>
       </c>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="35"/>
-    </row>
-    <row r="5" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="18"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="49"/>
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="20">
         <v>23</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="36" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="39">
-        <v>0</v>
-      </c>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="37"/>
-    </row>
-    <row r="6" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="23">
+        <v>0</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
+    </row>
+    <row r="6" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="49"/>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="20">
         <v>19</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="36" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="39">
-        <v>0</v>
-      </c>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="37"/>
-    </row>
-    <row r="7" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="23">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+    </row>
+    <row r="7" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="50"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="36">
-        <v>0</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="36">
+      <c r="C7" s="20">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="20">
         <v>14</v>
       </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="39">
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="23">
         <v>3</v>
       </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="37"/>
-    </row>
-    <row r="8" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+    </row>
+    <row r="8" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="48" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="20">
         <v>18</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="36">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="20">
         <v>1</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="39">
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="23">
         <v>3</v>
       </c>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="32"/>
-      <c r="T8" s="37"/>
-    </row>
-    <row r="9" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+    </row>
+    <row r="9" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="49"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="20">
         <v>43</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="36">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="20">
         <v>17</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="39">
-        <v>0</v>
-      </c>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="37"/>
-    </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="23">
+        <v>0</v>
+      </c>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+    </row>
+    <row r="10" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="49"/>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="36">
-        <v>0</v>
-      </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="36">
+      <c r="C10" s="20">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="20">
         <v>3</v>
       </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="37"/>
-      <c r="O10" s="39">
-        <v>0</v>
-      </c>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="37"/>
-    </row>
-    <row r="11" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="23">
+        <v>0</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+    </row>
+    <row r="11" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="50"/>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="36">
-        <v>0</v>
-      </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="36">
-        <v>0</v>
-      </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="39">
-        <v>0</v>
-      </c>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="37"/>
-    </row>
-    <row r="12" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="C11" s="20">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="20">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="23">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+    </row>
+    <row r="12" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="45" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="20">
         <v>7</v>
       </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="36">
-        <v>0</v>
-      </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="37"/>
-      <c r="O12" s="39">
-        <v>0</v>
-      </c>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="32"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="37"/>
-    </row>
-    <row r="13" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="20">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="23">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+    </row>
+    <row r="13" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46"/>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="36">
-        <v>0</v>
-      </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="36">
-        <v>0</v>
-      </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="37"/>
-      <c r="O13" s="39">
-        <v>0</v>
-      </c>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="37"/>
-    </row>
-    <row r="14" spans="1:20" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
+      <c r="C13" s="20">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="20">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="23">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+    </row>
+    <row r="14" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="46"/>
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="20">
         <v>6</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="36">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="20">
         <v>3</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="37"/>
-      <c r="O14" s="39">
-        <v>0</v>
-      </c>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="32"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="32"/>
-      <c r="T14" s="37"/>
-    </row>
-    <row r="15" spans="1:20" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="23">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+    </row>
+    <row r="15" spans="1:25" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="46"/>
       <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="20">
         <v>7</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="36">
-        <v>0</v>
-      </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="39">
-        <v>0</v>
-      </c>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="37"/>
-    </row>
-    <row r="16" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="22"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="20">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="23">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+    </row>
+    <row r="16" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="47"/>
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="43">
-        <v>0</v>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="43">
-        <v>0</v>
-      </c>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="45"/>
-      <c r="O16" s="46">
+      <c r="C16" s="27">
+        <v>0</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="27">
+        <v>0</v>
+      </c>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="30">
         <v>1</v>
       </c>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="44"/>
-      <c r="S16" s="44"/>
-      <c r="T16" s="45"/>
-    </row>
-    <row r="17" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
-      <c r="B17" s="40" t="s">
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+    </row>
+    <row r="17" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="57"/>
+      <c r="B17" s="24" t="s">
         <v>22</v>
       </c>
       <c r="C17" s="6">
@@ -1546,7 +1637,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="48">
+      <c r="I17" s="32">
         <v>25</v>
       </c>
       <c r="J17" s="9"/>
@@ -1554,7 +1645,7 @@
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="49">
+      <c r="O17" s="33">
         <v>30</v>
       </c>
       <c r="P17" s="9"/>
@@ -1562,76 +1653,198 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
       <c r="T17" s="10"/>
-    </row>
-    <row r="18" spans="1:20" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
-      <c r="B18" s="41" t="s">
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+    </row>
+    <row r="18" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="38"/>
+      <c r="B18" s="25" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="7">
         <f>SUM(C4:C16)</f>
         <v>140</v>
       </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="47">
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="31">
         <f>SUM(I4:I16)</f>
         <v>38</v>
       </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="47">
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="31">
         <f>SUM(O4:O16)</f>
         <v>8</v>
       </c>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="31"/>
-    </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="29"/>
-      <c r="B19" s="42" t="s">
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+    </row>
+    <row r="19" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="38"/>
+      <c r="B19" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="8">
         <v>2.3076923076923075</v>
       </c>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51">
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="35">
         <v>1.9230769230769231</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="52">
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="36">
         <v>2.3076923076923075</v>
       </c>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="53"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="37"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A20" s="38"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="55"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="55"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="55"/>
+      <c r="P20" s="55"/>
+      <c r="Q20" s="55"/>
+      <c r="R20" s="55"/>
+      <c r="S20" s="55"/>
+      <c r="T20" s="55"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A21" s="38"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="54"/>
+      <c r="K21" s="54"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="54"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A22" s="38"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="38"/>
+      <c r="X22" s="38"/>
+      <c r="Y22" s="38"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A23" s="38"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A17:A20"/>
+  <mergeCells count="12">
+    <mergeCell ref="B20:T23"/>
+    <mergeCell ref="A17:A23"/>
+    <mergeCell ref="U1:Y23"/>
     <mergeCell ref="O2:T2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="C2:H2"/>
@@ -1642,6 +1855,18 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
+  <conditionalFormatting sqref="C4:C16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="$I$19/2"/>
+        <cfvo type="formula" val="$H$19"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I4:I16">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -1666,18 +1891,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C16">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="formula" val="$I$19/2"/>
-        <cfvo type="formula" val="$H$19"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>

--- a/data/Heat map 4-2 Recognition and Reputation.xlsx
+++ b/data/Heat map 4-2 Recognition and Reputation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Learning\Miscellaneous\KPIDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF828658-3A8A-4F08-885C-CEBE3D0559BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8023A009-1E18-4088-9F03-221E65EB1C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{60C6FB9E-1B92-4818-B8F8-C10D82D4AFAC}"/>
   </bookViews>
@@ -558,7 +558,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -571,15 +571,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -619,12 +610,6 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -643,30 +628,21 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -715,14 +691,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1034,817 +1018,816 @@
   <cols>
     <col min="1" max="1" width="16.21875" customWidth="1"/>
     <col min="2" max="2" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="20" width="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="8.88671875" style="56"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="2" customFormat="1" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="44"/>
-      <c r="U1" s="38"/>
-      <c r="V1" s="38"/>
-      <c r="W1" s="38"/>
-      <c r="X1" s="38"/>
-      <c r="Y1" s="38"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="50"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
     </row>
     <row r="2" spans="1:25" s="1" customFormat="1" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52" t="s">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="39" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="39" t="s">
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
     </row>
     <row r="3" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="51"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="12" t="s">
+      <c r="I3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="12" t="s">
+      <c r="O3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="12" t="s">
+      <c r="S3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="13" t="s">
+      <c r="T3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="38"/>
-      <c r="V3" s="38"/>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
     </row>
     <row r="4" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="14">
         <v>17</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="17" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="22">
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="14">
         <v>1</v>
       </c>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18"/>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
     </row>
     <row r="5" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+      <c r="A5" s="41"/>
       <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="17">
         <v>23</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="20" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="21"/>
-      <c r="O5" s="23">
-        <v>0</v>
-      </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="17">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
     </row>
     <row r="6" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="41"/>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="17">
         <v>19</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="20" t="s">
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="23">
-        <v>0</v>
-      </c>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="17">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
     </row>
     <row r="7" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="50"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="20">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="20">
+      <c r="C7" s="17">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="17">
         <v>14</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="23">
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="17">
         <v>3</v>
       </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="21"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
     </row>
     <row r="8" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="40" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="17">
         <v>18</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="20">
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="17">
         <v>1</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="23">
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="17">
         <v>3</v>
       </c>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="21"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
     </row>
     <row r="9" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="41"/>
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="17">
         <v>43</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="20">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="17">
         <v>17</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="23">
-        <v>0</v>
-      </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="17">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
     </row>
     <row r="10" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="20">
-        <v>0</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="20">
+      <c r="C10" s="17">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="17">
         <v>3</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="21"/>
-      <c r="O10" s="23">
-        <v>0</v>
-      </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="21"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="17">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
     </row>
     <row r="11" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="50"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="20">
-        <v>0</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="20">
-        <v>0</v>
-      </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="23">
-        <v>0</v>
-      </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="21"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
+      <c r="C11" s="17">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="17">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="17">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
     </row>
     <row r="12" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="37" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="17">
         <v>7</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="20">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="23">
-        <v>0</v>
-      </c>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="21"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="17">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="17">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
     </row>
     <row r="13" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
+      <c r="A13" s="38"/>
       <c r="B13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="20">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="20">
-        <v>0</v>
-      </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="23">
-        <v>0</v>
-      </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
+      <c r="C13" s="17">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
     </row>
     <row r="14" spans="1:25" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
+      <c r="A14" s="38"/>
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="17">
         <v>6</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="20">
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="17">
         <v>3</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="23">
-        <v>0</v>
-      </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="17">
+        <v>0</v>
+      </c>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="18"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
     </row>
     <row r="15" spans="1:25" s="1" customFormat="1" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="17">
         <v>7</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="20">
-        <v>0</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="23">
-        <v>0</v>
-      </c>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="38"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="17">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="17">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
+      <c r="Y15" s="30"/>
     </row>
     <row r="16" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="47"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="27">
-        <v>0</v>
-      </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="27">
-        <v>0</v>
-      </c>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-      <c r="M16" s="28"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="30">
+      <c r="C16" s="22">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="22">
+        <v>0</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="22">
         <v>1</v>
       </c>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="38"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="38"/>
-      <c r="Y16" s="38"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="50"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
     </row>
     <row r="17" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57"/>
-      <c r="B17" s="24" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="46">
         <v>30</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="32">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="25">
         <v>25</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="33">
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="25">
         <v>30</v>
       </c>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="38"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="38"/>
-      <c r="Y17" s="38"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="50"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
     </row>
     <row r="18" spans="1:25" s="2" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
-      <c r="B18" s="25" t="s">
+      <c r="A18" s="30"/>
+      <c r="B18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="47">
         <f>SUM(C4:C16)</f>
         <v>140</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="31">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="49">
         <f>SUM(I4:I16)</f>
         <v>38</v>
       </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="31">
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="49">
         <f>SUM(O4:O16)</f>
         <v>8</v>
       </c>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="38"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="38"/>
-      <c r="Y18" s="38"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="50"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
     </row>
     <row r="19" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="38"/>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="48">
         <v>2.3076923076923075</v>
       </c>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35">
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="27">
         <v>1.9230769230769231</v>
       </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="36">
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="27">
         <v>2.3076923076923075</v>
       </c>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="38"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="38"/>
-      <c r="Y19" s="38"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A20" s="38"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="55"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="38"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="38"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
+      <c r="W20" s="51"/>
+      <c r="X20" s="51"/>
+      <c r="Y20" s="51"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="54"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="54"/>
-      <c r="O21" s="54"/>
-      <c r="P21" s="54"/>
-      <c r="Q21" s="54"/>
-      <c r="R21" s="54"/>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="51"/>
+      <c r="V21" s="51"/>
+      <c r="W21" s="51"/>
+      <c r="X21" s="51"/>
+      <c r="Y21" s="51"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
-      <c r="B22" s="54"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="54"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="38"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="38"/>
-      <c r="X22" s="38"/>
-      <c r="Y22" s="38"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="51"/>
+      <c r="R22" s="51"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="51"/>
+      <c r="V22" s="51"/>
+      <c r="W22" s="51"/>
+      <c r="X22" s="51"/>
+      <c r="Y22" s="51"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="51"/>
+      <c r="N23" s="51"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="51"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="51"/>
+      <c r="V23" s="51"/>
+      <c r="W23" s="51"/>
+      <c r="X23" s="51"/>
+      <c r="Y23" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B20:T23"/>
     <mergeCell ref="A17:A23"/>
-    <mergeCell ref="U1:Y23"/>
     <mergeCell ref="O2:T2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="C2:H2"/>
@@ -1854,6 +1837,8 @@
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U1:Y19"/>
+    <mergeCell ref="B20:Y23"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C16">
     <cfRule type="colorScale" priority="1">
